--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -1933,7 +1933,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>118666887</v>
       </c>
       <c r="B11" t="n">
-        <v>101008</v>
+        <v>101015</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Annelie Andersson</t>
+          <t>Annelie Andersson, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 23402-2021 artfynd.xlsx
+++ b/artfynd/A 23402-2021 artfynd.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annelie Andersson, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Annelie Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
